--- a/docs/AI/Project_Tracker.xlsx
+++ b/docs/AI/Project_Tracker.xlsx
@@ -4402,7 +4402,7 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">SUMPRODUCT('Phase Tracker'!$E$2:$E$7,'Phase Tracker'!$D$2:$D$7)</f>
-        <v>0.542</v>
+        <v>0.568</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1</v>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">'Phase Tracker'!E3</f>
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="I9" s="0" t="s">
         <v>25</v>
@@ -4573,7 +4573,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C14" s="5" t="n">
         <f aca="false">B15</f>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">B7</f>
-        <v>0.542</v>
+        <v>0.568</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>1</v>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E3" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$E$2:$E$200=A3)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$E$2:$E$200,A3),0)</f>
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="F3" s="11" t="str">
         <f aca="false">IF(E3=1,"✅ Completed",IF(E3&gt;0,"🔄 In Progress","⏳ Planned"))</f>
@@ -5917,11 +5917,11 @@
       <c r="I10" s="12"/>
       <c r="J10" s="15" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$D$2:$D$200=B10)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$D$2:$D$200,B10),0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K10" s="12" t="str">
         <f aca="false">IF(COUNTIFS(Epics!$B$2:$B$100,B10,Epics!$K$2:$K$100,"*Blocked*")&gt;0,"🚫 Blocked",IF(J10=1,"✅ Completed",IF(J10&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>🔄 In Progress</v>
       </c>
       <c r="L10" s="12" t="n">
         <v>0</v>
@@ -6865,11 +6865,11 @@
       <c r="I16" s="10"/>
       <c r="J16" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$C$2:$C$200=C16)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$C$2:$C$200,C16),0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K16" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$C$2:$C$200,C16,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(J16=1,"✅ Completed",IF(J16&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>🔄 In Progress</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8035,15 +8035,15 @@
       </c>
       <c r="H10" s="10" t="n">
         <f aca="false">SUMPRODUCT((Stories!$B$2:$B$200=A10)*(Stories!$P$2:$P$200))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="11" t="n">
         <f aca="false">IFERROR(H10/G10,0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J10" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$B$2:$B$200,A10,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(I10=1,"✅ Completed",IF(I10&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>🔄 In Progress</v>
       </c>
       <c r="K10" s="10" t="s">
         <v>87</v>
@@ -10441,7 +10441,7 @@
       <c r="K36" s="10"/>
       <c r="L36" s="10"/>
       <c r="M36" s="10" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="N36" s="10"/>
       <c r="O36" s="10" t="s">

--- a/docs/AI/Project_Tracker.xlsx
+++ b/docs/AI/Project_Tracker.xlsx
@@ -4402,7 +4402,7 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">SUMPRODUCT('Phase Tracker'!$E$2:$E$7,'Phase Tracker'!$D$2:$D$7)</f>
-        <v>0.568</v>
+        <v>0.594</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1</v>
@@ -4525,7 +4525,7 @@
         <v>30</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="5" t="n">
         <f aca="false">COUNTA(Milestones!$B$2:$B$25)</f>
@@ -4549,7 +4549,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" s="5" t="n">
         <f aca="false">COUNTA(Epics!$C$2:C$100)</f>
@@ -4573,7 +4573,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="5" t="n">
         <f aca="false">B15</f>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E3" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$E$2:$E$200=A3)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$E$2:$E$200,A3),0)</f>
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="F3" s="11" t="str">
         <f aca="false">IF(E3=1,"✅ Completed",IF(E3&gt;0,"🔄 In Progress","⏳ Planned"))</f>
@@ -5917,11 +5917,11 @@
       <c r="I10" s="12"/>
       <c r="J10" s="15" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$D$2:$D$200=B10)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$D$2:$D$200,B10),0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K10" s="12" t="str">
         <f aca="false">IF(COUNTIFS(Epics!$B$2:$B$100,B10,Epics!$K$2:$K$100,"*Blocked*")&gt;0,"🚫 Blocked",IF(J10=1,"✅ Completed",IF(J10&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>🔄 In Progress</v>
+        <v>✅ Completed</v>
       </c>
       <c r="L10" s="12" t="n">
         <v>0</v>
@@ -6865,11 +6865,11 @@
       <c r="I16" s="10"/>
       <c r="J16" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$C$2:$C$200=C16)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$C$2:$C$200,C16),0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K16" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$C$2:$C$200,C16,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(J16=1,"✅ Completed",IF(J16&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>🔄 In Progress</v>
+        <v>✅ Completed</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8035,15 +8035,15 @@
       </c>
       <c r="H10" s="10" t="n">
         <f aca="false">SUMPRODUCT((Stories!$B$2:$B$200=A10)*(Stories!$P$2:$P$200))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" s="11" t="n">
         <f aca="false">IFERROR(H10/G10,0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J10" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$B$2:$B$200,A10,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(I10=1,"✅ Completed",IF(I10&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>🔄 In Progress</v>
+        <v>✅ Completed</v>
       </c>
       <c r="K10" s="10" t="s">
         <v>87</v>
@@ -10484,7 +10484,7 @@
       <c r="K37" s="10"/>
       <c r="L37" s="10"/>
       <c r="M37" s="10" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="N37" s="10"/>
       <c r="O37" s="10" t="s">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="P37" s="10" t="n">
         <f aca="false">IF(ISNUMBER(SEARCH("Done",M37)),1,IF(ISNUMBER(SEARCH("In Progress",M37)),0.5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="66" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">

--- a/docs/AI/Project_Tracker.xlsx
+++ b/docs/AI/Project_Tracker.xlsx
@@ -4402,7 +4402,7 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">SUMPRODUCT('Phase Tracker'!$E$2:$E$7,'Phase Tracker'!$D$2:$D$7)</f>
-        <v>0.594</v>
+        <v>0.62</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1</v>
@@ -4573,7 +4573,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C14" s="5" t="n">
         <f aca="false">B15</f>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E3" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$E$2:$E$200=A3)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$E$2:$E$200,A3),0)</f>
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="F3" s="11" t="str">
         <f aca="false">IF(E3=1,"✅ Completed",IF(E3&gt;0,"🔄 In Progress","⏳ Planned"))</f>
@@ -5949,11 +5949,11 @@
       <c r="I11" s="12"/>
       <c r="J11" s="15" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$D$2:$D$200=B11)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$D$2:$D$200,B11),0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K11" s="12" t="str">
         <f aca="false">IF(COUNTIFS(Epics!$B$2:$B$100,B11,Epics!$K$2:$K$100,"*Blocked*")&gt;0,"🚫 Blocked",IF(J11=1,"✅ Completed",IF(J11&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>🔄 In Progress</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>0</v>
@@ -6894,11 +6894,11 @@
       <c r="I17" s="10"/>
       <c r="J17" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$C$2:$C$200=C17)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$C$2:$C$200,C17),0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K17" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$C$2:$C$200,C17,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(J17=1,"✅ Completed",IF(J17&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>🔄 In Progress</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8074,15 +8074,15 @@
       </c>
       <c r="H11" s="10" t="n">
         <f aca="false">SUMPRODUCT((Stories!$B$2:$B$200=A11)*(Stories!$P$2:$P$200))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="11" t="n">
         <f aca="false">IFERROR(H11/G11,0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J11" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$B$2:$B$200,A11,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(I11=1,"✅ Completed",IF(I11&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>🔄 In Progress</v>
       </c>
       <c r="K11" s="10" t="s">
         <v>90</v>
@@ -10527,7 +10527,7 @@
       <c r="K38" s="10"/>
       <c r="L38" s="10"/>
       <c r="M38" s="10" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="N38" s="10"/>
       <c r="O38" s="10" t="s">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="P38" s="10" t="n">
         <f aca="false">IF(ISNUMBER(SEARCH("Done",M38)),1,IF(ISNUMBER(SEARCH("In Progress",M38)),0.5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="52.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">

--- a/docs/AI/Project_Tracker.xlsx
+++ b/docs/AI/Project_Tracker.xlsx
@@ -4421,7 +4421,7 @@
         <v>19</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4493,7 +4493,7 @@
         <v>28</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/docs/AI/Project_Tracker.xlsx
+++ b/docs/AI/Project_Tracker.xlsx
@@ -4402,7 +4402,7 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">SUMPRODUCT('Phase Tracker'!$E$2:$E$7,'Phase Tracker'!$D$2:$D$7)</f>
-        <v>0.62</v>
+        <v>0.646</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1</v>
@@ -4421,7 +4421,7 @@
         <v>19</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4493,7 +4493,7 @@
         <v>28</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4525,7 +4525,7 @@
         <v>30</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" s="5" t="n">
         <f aca="false">COUNTA(Milestones!$B$2:$B$25)</f>
@@ -4549,7 +4549,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" s="5" t="n">
         <f aca="false">COUNTA(Epics!$C$2:C$100)</f>
@@ -4573,7 +4573,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" s="5" t="n">
         <f aca="false">B15</f>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E3" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$E$2:$E$200=A3)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$E$2:$E$200,A3),0)</f>
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="F3" s="11" t="str">
         <f aca="false">IF(E3=1,"✅ Completed",IF(E3&gt;0,"🔄 In Progress","⏳ Planned"))</f>
@@ -5949,11 +5949,11 @@
       <c r="I11" s="12"/>
       <c r="J11" s="15" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$D$2:$D$200=B11)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$D$2:$D$200,B11),0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K11" s="12" t="str">
         <f aca="false">IF(COUNTIFS(Epics!$B$2:$B$100,B11,Epics!$K$2:$K$100,"*Blocked*")&gt;0,"🚫 Blocked",IF(J11=1,"✅ Completed",IF(J11&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>🔄 In Progress</v>
+        <v>✅ Completed</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>0</v>
@@ -6894,11 +6894,11 @@
       <c r="I17" s="10"/>
       <c r="J17" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$C$2:$C$200=C17)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$C$2:$C$200,C17),0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K17" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$C$2:$C$200,C17,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(J17=1,"✅ Completed",IF(J17&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>🔄 In Progress</v>
+        <v>✅ Completed</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8074,15 +8074,15 @@
       </c>
       <c r="H11" s="10" t="n">
         <f aca="false">SUMPRODUCT((Stories!$B$2:$B$200=A11)*(Stories!$P$2:$P$200))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" s="11" t="n">
         <f aca="false">IFERROR(H11/G11,0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J11" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$B$2:$B$200,A11,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(I11=1,"✅ Completed",IF(I11&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>🔄 In Progress</v>
+        <v>✅ Completed</v>
       </c>
       <c r="K11" s="10" t="s">
         <v>90</v>
@@ -10570,7 +10570,7 @@
       <c r="K39" s="10"/>
       <c r="L39" s="10"/>
       <c r="M39" s="10" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="N39" s="10"/>
       <c r="O39" s="10" t="s">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="P39" s="10" t="n">
         <f aca="false">IF(ISNUMBER(SEARCH("Done",M39)),1,IF(ISNUMBER(SEARCH("In Progress",M39)),0.5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="78.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">

--- a/docs/AI/Project_Tracker.xlsx
+++ b/docs/AI/Project_Tracker.xlsx
@@ -4402,7 +4402,7 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">SUMPRODUCT('Phase Tracker'!$E$2:$E$7,'Phase Tracker'!$D$2:$D$7)</f>
-        <v>0.646</v>
+        <v>0.672</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1</v>
@@ -4421,7 +4421,7 @@
         <v>19</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4493,7 +4493,7 @@
         <v>28</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4573,7 +4573,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" s="5" t="n">
         <f aca="false">B15</f>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E3" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$E$2:$E$200=A3)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$E$2:$E$200,A3),0)</f>
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="F3" s="11" t="str">
         <f aca="false">IF(E3=1,"✅ Completed",IF(E3&gt;0,"🔄 In Progress","⏳ Planned"))</f>
@@ -5981,11 +5981,11 @@
       <c r="I12" s="12"/>
       <c r="J12" s="15" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$D$2:$D$200=B12)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$D$2:$D$200,B12),0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K12" s="12" t="str">
         <f aca="false">IF(COUNTIFS(Epics!$B$2:$B$100,B12,Epics!$K$2:$K$100,"*Blocked*")&gt;0,"🚫 Blocked",IF(J12=1,"✅ Completed",IF(J12&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>🔄 In Progress</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>0</v>
@@ -6923,11 +6923,11 @@
       <c r="I18" s="10"/>
       <c r="J18" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$C$2:$C$200=C18)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$C$2:$C$200,C18),0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K18" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$C$2:$C$200,C18,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(J18=1,"✅ Completed",IF(J18&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>🔄 In Progress</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8113,15 +8113,15 @@
       </c>
       <c r="H12" s="10" t="n">
         <f aca="false">SUMPRODUCT((Stories!$B$2:$B$200=A12)*(Stories!$P$2:$P$200))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="11" t="n">
         <f aca="false">IFERROR(H12/G12,0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J12" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$B$2:$B$200,A12,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(I12=1,"✅ Completed",IF(I12&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>🔄 In Progress</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>93</v>
@@ -10613,7 +10613,7 @@
       <c r="K40" s="10"/>
       <c r="L40" s="10"/>
       <c r="M40" s="10" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="N40" s="10"/>
       <c r="O40" s="10" t="s">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="P40" s="10" t="n">
         <f aca="false">IF(ISNUMBER(SEARCH("Done",M40)),1,IF(ISNUMBER(SEARCH("In Progress",M40)),0.5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="66" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">

--- a/docs/AI/Project_Tracker.xlsx
+++ b/docs/AI/Project_Tracker.xlsx
@@ -4402,7 +4402,7 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">SUMPRODUCT('Phase Tracker'!$E$2:$E$7,'Phase Tracker'!$D$2:$D$7)</f>
-        <v>0.672</v>
+        <v>0.698</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1</v>
@@ -4421,7 +4421,7 @@
         <v>19</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4493,7 +4493,7 @@
         <v>28</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4525,7 +4525,7 @@
         <v>30</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" s="5" t="n">
         <f aca="false">COUNTA(Milestones!$B$2:$B$25)</f>
@@ -4549,7 +4549,7 @@
         <v>31</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" s="5" t="n">
         <f aca="false">COUNTA(Epics!$C$2:C$100)</f>
@@ -4573,7 +4573,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" s="5" t="n">
         <f aca="false">B15</f>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E3" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$E$2:$E$200=A3)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$E$2:$E$200,A3),0)</f>
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="F3" s="11" t="str">
         <f aca="false">IF(E3=1,"✅ Completed",IF(E3&gt;0,"🔄 In Progress","⏳ Planned"))</f>
@@ -5981,11 +5981,11 @@
       <c r="I12" s="12"/>
       <c r="J12" s="15" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$D$2:$D$200=B12)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$D$2:$D$200,B12),0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K12" s="12" t="str">
         <f aca="false">IF(COUNTIFS(Epics!$B$2:$B$100,B12,Epics!$K$2:$K$100,"*Blocked*")&gt;0,"🚫 Blocked",IF(J12=1,"✅ Completed",IF(J12&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>🔄 In Progress</v>
+        <v>✅ Completed</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>0</v>
@@ -6923,11 +6923,11 @@
       <c r="I18" s="10"/>
       <c r="J18" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$C$2:$C$200=C18)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$C$2:$C$200,C18),0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K18" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$C$2:$C$200,C18,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(J18=1,"✅ Completed",IF(J18&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>🔄 In Progress</v>
+        <v>✅ Completed</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8113,15 +8113,15 @@
       </c>
       <c r="H12" s="10" t="n">
         <f aca="false">SUMPRODUCT((Stories!$B$2:$B$200=A12)*(Stories!$P$2:$P$200))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="11" t="n">
         <f aca="false">IFERROR(H12/G12,0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J12" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$B$2:$B$200,A12,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(I12=1,"✅ Completed",IF(I12&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>🔄 In Progress</v>
+        <v>✅ Completed</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>93</v>
@@ -10656,7 +10656,7 @@
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
       <c r="M41" s="10" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="N41" s="10"/>
       <c r="O41" s="10" t="s">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="P41" s="10" t="n">
         <f aca="false">IF(ISNUMBER(SEARCH("Done",M41)),1,IF(ISNUMBER(SEARCH("In Progress",M41)),0.5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="78.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">

--- a/docs/AI/Project_Tracker.xlsx
+++ b/docs/AI/Project_Tracker.xlsx
@@ -4402,7 +4402,7 @@
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">SUMPRODUCT('Phase Tracker'!$E$2:$E$7,'Phase Tracker'!$D$2:$D$7)</f>
-        <v>0.698</v>
+        <v>0.724</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1</v>
@@ -4421,7 +4421,7 @@
         <v>19</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4453,7 +4453,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -4477,7 +4477,7 @@
         <v>26</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -4493,7 +4493,7 @@
         <v>28</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4573,7 +4573,7 @@
         <v>32</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C14" s="5" t="n">
         <f aca="false">B15</f>
@@ -4622,7 +4622,7 @@
         <v>36</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="E3" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$E$2:$E$200=A3)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$E$2:$E$200,A3),0)</f>
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="F3" s="11" t="str">
         <f aca="false">IF(E3=1,"✅ Completed",IF(E3&gt;0,"🔄 In Progress","⏳ Planned"))</f>
@@ -6013,11 +6013,11 @@
       <c r="I13" s="12"/>
       <c r="J13" s="15" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$D$2:$D$200=B13)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$D$2:$D$200,B13),0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K13" s="12" t="str">
         <f aca="false">IF(COUNTIFS(Epics!$B$2:$B$100,B13,Epics!$K$2:$K$100,"*Blocked*")&gt;0,"🚫 Blocked",IF(J13=1,"✅ Completed",IF(J13&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>🔄 In Progress</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>0</v>
@@ -6952,11 +6952,11 @@
       <c r="I19" s="10"/>
       <c r="J19" s="11" t="n">
         <f aca="false">IFERROR(SUMPRODUCT((Stories!$C$2:$C$200=C19)*(Stories!$P$2:$P$200))/COUNTIF(Stories!$C$2:$C$200,C19),0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K19" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$C$2:$C$200,C19,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(J19=1,"✅ Completed",IF(J19&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>🔄 In Progress</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8152,15 +8152,15 @@
       </c>
       <c r="H13" s="10" t="n">
         <f aca="false">SUMPRODUCT((Stories!$B$2:$B$200=A13)*(Stories!$P$2:$P$200))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="11" t="n">
         <f aca="false">IFERROR(H13/G13,0)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J13" s="11" t="str">
         <f aca="false">IF(COUNTIFS(Stories!$B$2:$B$200,A13,Stories!$M$2:$M$200,"*Blocked*")&gt;0,"🚫 Blocked",IF(I13=1,"✅ Completed",IF(I13&gt;0,"🔄 In Progress","⏳ Planned")))</f>
-        <v>⏳ Planned</v>
+        <v>🔄 In Progress</v>
       </c>
       <c r="K13" s="10" t="s">
         <v>96</v>
@@ -10277,7 +10277,7 @@
       </c>
       <c r="P32" s="10" t="n">
         <f aca="false">IF(ISNUMBER(SEARCH("Done",M32)),1,IF(ISNUMBER(SEARCH("In Progress",M32)),0.5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="78.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="P33" s="10" t="n">
         <f aca="false">IF(ISNUMBER(SEARCH("Done",M33)),1,IF(ISNUMBER(SEARCH("In Progress",M33)),0.5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="78.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="P34" s="10" t="n">
         <f aca="false">IF(ISNUMBER(SEARCH("Done",M34)),1,IF(ISNUMBER(SEARCH("In Progress",M34)),0.5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="78.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="P35" s="10" t="n">
         <f aca="false">IF(ISNUMBER(SEARCH("Done",M35)),1,IF(ISNUMBER(SEARCH("In Progress",M35)),0.5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="78.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="P36" s="10" t="n">
         <f aca="false">IF(ISNUMBER(SEARCH("Done",M36)),1,IF(ISNUMBER(SEARCH("In Progress",M36)),0.5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="66" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10699,7 +10699,7 @@
       <c r="K42" s="10"/>
       <c r="L42" s="10"/>
       <c r="M42" s="10" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="N42" s="10"/>
       <c r="O42" s="10" t="s">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="P42" s="10" t="n">
         <f aca="false">IF(ISNUMBER(SEARCH("Done",M42)),1,IF(ISNUMBER(SEARCH("In Progress",M42)),0.5,0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="66" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
